--- a/excel-files/CALOOCAN/KASARINLAN ELEMENTARY SCHOOL.xlsx
+++ b/excel-files/CALOOCAN/KASARINLAN ELEMENTARY SCHOOL.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29711"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29917"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="398" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9B5DF313-AD75-4684-9A40-03FFF4623020}"/>
+  <xr:revisionPtr revIDLastSave="461" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AD47E5A2-E10C-45A3-96BE-FAEB84AC8F1B}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="100">
   <si>
     <t>Grade Level</t>
   </si>
@@ -67,6 +67,9 @@
     <t>Reading and Literacy</t>
   </si>
   <si>
+    <t>RO</t>
+  </si>
+  <si>
     <t>Language</t>
   </si>
   <si>
@@ -86,9 +89,6 @@
   </si>
   <si>
     <t>Filipino</t>
-  </si>
-  <si>
-    <t>RO</t>
   </si>
   <si>
     <t>Araling Panlipunan</t>
@@ -783,6 +783,20 @@
     <xf numFmtId="0" fontId="5" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -794,20 +808,6 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3567,16 +3567,22 @@
       <c r="C2" s="1">
         <v>379</v>
       </c>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="5"/>
+      <c r="D2" s="1">
+        <v>631</v>
+      </c>
+      <c r="E2" s="1">
+        <v>2024</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="G2" s="3">
         <f>IF((C2-D2)&lt;0,0,C2-D2)</f>
-        <v>379</v>
+        <v>0</v>
       </c>
       <c r="H2" s="4">
         <f>IF((D2-C2)&lt;0,0,D2-C2)</f>
-        <v>0</v>
+        <v>252</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="29.25" customHeight="1">
@@ -3584,7 +3590,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C3" s="1">
         <v>379</v>
@@ -3606,21 +3612,27 @@
         <v>1</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1">
         <v>379</v>
       </c>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="5"/>
+      <c r="D4" s="1">
+        <v>631</v>
+      </c>
+      <c r="E4" s="1">
+        <v>2024</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="G4" s="3">
         <f>IF((C4-D4)&lt;0,0,C4-D4)</f>
-        <v>379</v>
+        <v>0</v>
       </c>
       <c r="H4" s="4">
         <f>IF((D4-C4)&lt;0,0,D4-C4)</f>
-        <v>0</v>
+        <v>252</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="25.5" customHeight="1">
@@ -3628,21 +3640,27 @@
         <v>1</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C5" s="1">
         <v>379</v>
       </c>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="5"/>
+      <c r="D5" s="1">
+        <v>631</v>
+      </c>
+      <c r="E5" s="1">
+        <v>2025</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="G5" s="3">
         <f t="shared" ref="G5:G6" si="0">IF((C5-D5)&lt;0,0,C5-D5)</f>
-        <v>379</v>
+        <v>0</v>
       </c>
       <c r="H5" s="4">
         <f t="shared" ref="H5:H6" si="1">IF((D5-C5)&lt;0,0,D5-C5)</f>
-        <v>0</v>
+        <v>252</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="19.5">
@@ -3650,7 +3668,7 @@
         <v>1</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C6" s="1">
         <v>379</v>
@@ -3699,7 +3717,7 @@
         <v>2</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C9" s="1">
         <v>440</v>
@@ -3721,7 +3739,7 @@
         <v>2</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C10" s="1">
         <v>440</v>
@@ -3743,21 +3761,27 @@
         <v>2</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C11" s="1">
         <v>440</v>
       </c>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="5"/>
+      <c r="D11" s="1">
+        <v>500</v>
+      </c>
+      <c r="E11" s="1">
+        <v>2026</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="G11" s="3">
         <f>IF((C11-D11)&lt;0,0,C11-D11)</f>
-        <v>440</v>
+        <v>0</v>
       </c>
       <c r="H11" s="4">
         <f>IF((D11-C11)&lt;0,0,D11-C11)</f>
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="19.5">
@@ -3765,7 +3789,7 @@
         <v>2</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C12" s="1">
         <v>440</v>
@@ -3814,7 +3838,7 @@
         <v>3</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C15" s="1">
         <v>493</v>
@@ -3836,7 +3860,7 @@
         <v>3</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C16" s="1">
         <v>493</v>
@@ -3858,7 +3882,7 @@
         <v>3</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C17" s="1">
         <v>493</v>
@@ -3880,7 +3904,7 @@
         <v>3</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C18" s="1">
         <v>493</v>
@@ -3902,7 +3926,7 @@
         <v>3</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C19" s="1">
         <v>493</v>
@@ -3934,17 +3958,23 @@
         <v>4</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C21" s="1">
         <v>550</v>
       </c>
-      <c r="D21" s="1"/>
-      <c r="E21" s="1"/>
-      <c r="F21" s="5"/>
+      <c r="D21" s="1">
+        <v>494</v>
+      </c>
+      <c r="E21" s="1">
+        <v>2024</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="G21" s="3">
         <f t="shared" ref="G21:G29" si="4">IF((C21-D21)&lt;0,0,C21-D21)</f>
-        <v>550</v>
+        <v>56</v>
       </c>
       <c r="H21" s="4">
         <f t="shared" ref="H21:H29" si="5">IF((D21-C21)&lt;0,0,D21-C21)</f>
@@ -3956,17 +3986,23 @@
         <v>4</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C22" s="1">
         <v>550</v>
       </c>
-      <c r="D22" s="1"/>
-      <c r="E22" s="1"/>
-      <c r="F22" s="5"/>
+      <c r="D22" s="1">
+        <v>494</v>
+      </c>
+      <c r="E22" s="1">
+        <v>2024</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="G22" s="3">
         <f t="shared" si="4"/>
-        <v>550</v>
+        <v>56</v>
       </c>
       <c r="H22" s="4">
         <f t="shared" si="5"/>
@@ -3978,7 +4014,7 @@
         <v>4</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C23" s="1">
         <v>550</v>
@@ -3990,7 +4026,7 @@
         <v>2025</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="G23" s="3">
         <f t="shared" si="4"/>
@@ -4006,7 +4042,7 @@
         <v>4</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C24" s="1">
         <v>550</v>
@@ -4018,7 +4054,7 @@
         <v>2025</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="G24" s="3">
         <f t="shared" si="4"/>
@@ -4039,12 +4075,18 @@
       <c r="C25" s="1">
         <v>550</v>
       </c>
-      <c r="D25" s="1"/>
-      <c r="E25" s="1"/>
-      <c r="F25" s="5"/>
+      <c r="D25" s="1">
+        <v>494</v>
+      </c>
+      <c r="E25" s="1">
+        <v>2024</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="G25" s="3">
         <f t="shared" si="4"/>
-        <v>550</v>
+        <v>56</v>
       </c>
       <c r="H25" s="4">
         <f t="shared" si="5"/>
@@ -4056,17 +4098,23 @@
         <v>4</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C26" s="1">
         <v>550</v>
       </c>
-      <c r="D26" s="1"/>
-      <c r="E26" s="1"/>
-      <c r="F26" s="5"/>
+      <c r="D26" s="1">
+        <v>494</v>
+      </c>
+      <c r="E26" s="1">
+        <v>2024</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="G26" s="3">
         <f t="shared" si="4"/>
-        <v>550</v>
+        <v>56</v>
       </c>
       <c r="H26" s="4">
         <f t="shared" si="5"/>
@@ -4083,12 +4131,18 @@
       <c r="C27" s="1">
         <v>550</v>
       </c>
-      <c r="D27" s="1"/>
-      <c r="E27" s="1"/>
-      <c r="F27" s="5"/>
+      <c r="D27" s="1">
+        <v>550</v>
+      </c>
+      <c r="E27" s="1">
+        <v>2024</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="G27" s="3">
         <f t="shared" si="4"/>
-        <v>550</v>
+        <v>0</v>
       </c>
       <c r="H27" s="4">
         <f t="shared" si="5"/>
@@ -4127,12 +4181,18 @@
       <c r="C29" s="1">
         <v>550</v>
       </c>
-      <c r="D29" s="1"/>
-      <c r="E29" s="1"/>
-      <c r="F29" s="5"/>
+      <c r="D29" s="1">
+        <v>494</v>
+      </c>
+      <c r="E29" s="1">
+        <v>2026</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="G29" s="3">
         <f t="shared" si="4"/>
-        <v>550</v>
+        <v>56</v>
       </c>
       <c r="H29" s="4">
         <f t="shared" si="5"/>
@@ -4154,7 +4214,7 @@
         <v>5</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C31" s="1">
         <v>431</v>
@@ -4165,7 +4225,9 @@
       <c r="E31" s="1">
         <v>2025</v>
       </c>
-      <c r="F31" s="5"/>
+      <c r="F31" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="G31" s="3">
         <f t="shared" ref="G31:G39" si="6">IF((C31-D31)&lt;0,0,C31-D31)</f>
         <v>0</v>
@@ -4180,7 +4242,7 @@
         <v>5</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C32" s="1">
         <v>431</v>
@@ -4202,7 +4264,7 @@
         <v>5</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C33" s="1">
         <v>431</v>
@@ -4224,7 +4286,7 @@
         <v>5</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C34" s="1">
         <v>431</v>
@@ -4251,16 +4313,22 @@
       <c r="C35" s="1">
         <v>431</v>
       </c>
-      <c r="D35" s="1"/>
-      <c r="E35" s="1"/>
-      <c r="F35" s="5"/>
+      <c r="D35" s="1">
+        <v>530</v>
+      </c>
+      <c r="E35" s="1">
+        <v>2025</v>
+      </c>
+      <c r="F35" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="G35" s="3">
         <f t="shared" si="6"/>
-        <v>431</v>
+        <v>0</v>
       </c>
       <c r="H35" s="4">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>99</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="27.75" customHeight="1">
@@ -4268,7 +4336,7 @@
         <v>5</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C36" s="1">
         <v>431</v>
@@ -4280,7 +4348,7 @@
         <v>2025</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="G36" s="3">
         <f t="shared" si="6"/>
@@ -4308,7 +4376,7 @@
         <v>2025</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="G37" s="3">
         <f t="shared" si="6"/>
@@ -4329,16 +4397,22 @@
       <c r="C38" s="1">
         <v>431</v>
       </c>
-      <c r="D38" s="1"/>
-      <c r="E38" s="1"/>
-      <c r="F38" s="5"/>
+      <c r="D38" s="1">
+        <v>530</v>
+      </c>
+      <c r="E38" s="1">
+        <v>2026</v>
+      </c>
+      <c r="F38" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="G38" s="3">
         <f t="shared" si="6"/>
-        <v>431</v>
+        <v>0</v>
       </c>
       <c r="H38" s="4">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>99</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="27.75" customHeight="1">
@@ -4378,7 +4452,7 @@
         <v>6</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C41" s="1">
         <v>484</v>
@@ -4400,7 +4474,7 @@
         <v>6</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C42" s="1">
         <v>484</v>
@@ -4422,7 +4496,7 @@
         <v>6</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C43" s="1">
         <v>484</v>
@@ -4444,7 +4518,7 @@
         <v>6</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C44" s="1">
         <v>484</v>
@@ -4488,7 +4562,7 @@
         <v>6</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C46" s="1">
         <v>484</v>
@@ -4586,7 +4660,7 @@
         <v>7</v>
       </c>
       <c r="B51" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="10"/>
@@ -4606,7 +4680,7 @@
         <v>7</v>
       </c>
       <c r="B52" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C52" s="10"/>
       <c r="D52" s="10"/>
@@ -4626,7 +4700,7 @@
         <v>7</v>
       </c>
       <c r="B53" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="10"/>
@@ -4686,7 +4760,7 @@
         <v>7</v>
       </c>
       <c r="B56" s="11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C56" s="10"/>
       <c r="D56" s="10"/>
@@ -4776,7 +4850,7 @@
         <v>8</v>
       </c>
       <c r="B61" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="10"/>
@@ -4796,7 +4870,7 @@
         <v>8</v>
       </c>
       <c r="B62" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C62" s="10"/>
       <c r="D62" s="10"/>
@@ -4816,7 +4890,7 @@
         <v>8</v>
       </c>
       <c r="B63" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="10"/>
@@ -4876,7 +4950,7 @@
         <v>8</v>
       </c>
       <c r="B66" s="11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C66" s="10"/>
       <c r="D66" s="10"/>
@@ -4966,7 +5040,7 @@
         <v>9</v>
       </c>
       <c r="B71" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="10"/>
@@ -4986,7 +5060,7 @@
         <v>9</v>
       </c>
       <c r="B72" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C72" s="10"/>
       <c r="D72" s="10"/>
@@ -5006,7 +5080,7 @@
         <v>9</v>
       </c>
       <c r="B73" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="10"/>
@@ -5066,7 +5140,7 @@
         <v>9</v>
       </c>
       <c r="B76" s="11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C76" s="10"/>
       <c r="D76" s="10"/>
@@ -5156,7 +5230,7 @@
         <v>10</v>
       </c>
       <c r="B81" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="10"/>
@@ -5176,7 +5250,7 @@
         <v>10</v>
       </c>
       <c r="B82" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C82" s="10"/>
       <c r="D82" s="10"/>
@@ -5196,7 +5270,7 @@
         <v>10</v>
       </c>
       <c r="B83" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="10"/>
@@ -5256,7 +5330,7 @@
         <v>10</v>
       </c>
       <c r="B86" s="11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C86" s="10"/>
       <c r="D86" s="10"/>
@@ -5522,27 +5596,27 @@
       </c>
     </row>
     <row r="104" spans="1:8">
-      <c r="F104" s="46" t="s">
+      <c r="F104" s="42" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="105" spans="1:8">
-      <c r="F105" s="46" t="s">
+      <c r="F105" s="42" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="106" spans="1:8" ht="15">
-      <c r="C106" s="47" t="s">
+      <c r="C106" s="43" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="107" spans="1:8">
-      <c r="C107" s="46" t="s">
+      <c r="C107" s="42" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="108" spans="1:8">
-      <c r="C108" s="46" t="s">
+      <c r="C108" s="42" t="s">
         <v>41</v>
       </c>
     </row>
@@ -5553,8 +5627,8 @@
   </protectedRanges>
   <phoneticPr fontId="8" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E14:E19 E21:E29 E31:E39 E51:E59 E61:E69 E41:E49 E2:E6 E71:E79 E81:E89 E8:E12 E91:E98" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E91:E98 E81:E89 E71:E79 E61:E69 E51:E59 E41:E49 E31:E39 E21:E29 E14:E19 E8:E12 E2:E6" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F14:F19 F21:F29 F31:F39 F41:F49 F51:F59 F61:F69 F71:F79 F81:F89 F2:F6 F8:F12 F91:F98" xr:uid="{2F7388E0-D1A1-4571-8C10-96CB9A727EB3}">
       <formula1>"CO,RO,SDO"</formula1>
@@ -5569,18 +5643,19 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0858F8C8-8AF8-4852-B88C-61047AF726C8}">
-  <dimension ref="A1:AA157"/>
+  <dimension ref="A1:AA140"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
-    <col min="1" max="1" width="9.42578125" customWidth="1"/>
-    <col min="2" max="2" width="27.85546875" customWidth="1"/>
-    <col min="3" max="3" width="17.140625" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="26.140625" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="23.140625" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="24.85546875" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="18.5703125" hidden="1" customWidth="1"/>
-    <col min="8" max="9" width="20.85546875" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="13.7109375" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="38.42578125" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" customWidth="1"/>
+    <col min="3" max="3" width="13.7109375" customWidth="1"/>
+    <col min="4" max="4" width="10.5703125" customWidth="1"/>
+    <col min="5" max="5" width="19.28515625" customWidth="1"/>
+    <col min="6" max="6" width="16.28515625" customWidth="1"/>
+    <col min="7" max="7" width="15.42578125" customWidth="1"/>
+    <col min="8" max="8" width="54.28515625" customWidth="1"/>
+    <col min="9" max="9" width="27.140625" customWidth="1"/>
+    <col min="10" max="10" width="10.140625" customWidth="1"/>
     <col min="11" max="11" width="35.5703125" customWidth="1"/>
     <col min="12" max="12" width="24.85546875" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="31.5703125" customWidth="1"/>
@@ -5599,38 +5674,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1">
-      <c r="D1" s="42" t="s">
+      <c r="D1" s="48" t="s">
         <v>42</v>
       </c>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42"/>
-      <c r="H1" s="42"/>
-      <c r="I1" s="42"/>
-      <c r="J1" s="43" t="s">
+      <c r="E1" s="48"/>
+      <c r="F1" s="48"/>
+      <c r="G1" s="48"/>
+      <c r="H1" s="48"/>
+      <c r="I1" s="48"/>
+      <c r="J1" s="49" t="s">
         <v>43</v>
       </c>
-      <c r="K1" s="43"/>
-      <c r="L1" s="43"/>
-      <c r="M1" s="43"/>
-      <c r="N1" s="43"/>
-      <c r="O1" s="43"/>
-      <c r="P1" s="44" t="s">
+      <c r="K1" s="49"/>
+      <c r="L1" s="49"/>
+      <c r="M1" s="49"/>
+      <c r="N1" s="49"/>
+      <c r="O1" s="49"/>
+      <c r="P1" s="50" t="s">
         <v>44</v>
       </c>
-      <c r="Q1" s="44"/>
-      <c r="R1" s="44"/>
-      <c r="S1" s="44"/>
-      <c r="T1" s="44"/>
-      <c r="U1" s="44"/>
-      <c r="V1" s="45" t="s">
+      <c r="Q1" s="50"/>
+      <c r="R1" s="50"/>
+      <c r="S1" s="50"/>
+      <c r="T1" s="50"/>
+      <c r="U1" s="50"/>
+      <c r="V1" s="51" t="s">
         <v>45</v>
       </c>
-      <c r="W1" s="45"/>
-      <c r="X1" s="45"/>
-      <c r="Y1" s="45"/>
-      <c r="Z1" s="45"/>
-      <c r="AA1" s="45"/>
+      <c r="W1" s="51"/>
+      <c r="X1" s="51"/>
+      <c r="Y1" s="51"/>
+      <c r="Z1" s="51"/>
+      <c r="AA1" s="51"/>
     </row>
     <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1">
       <c r="A2" s="15" t="s">
@@ -5874,7 +5949,7 @@
         <v>1</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C6" s="1">
         <v>379</v>
@@ -5947,7 +6022,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C7" s="1">
         <v>379</v>
@@ -6020,7 +6095,7 @@
         <v>1</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C8" s="1">
         <v>379</v>
@@ -6093,7 +6168,7 @@
         <v>1</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C9" s="1">
         <v>379</v>
@@ -6166,7 +6241,7 @@
         <v>1</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C10" s="1">
         <v>379</v>
@@ -6239,7 +6314,7 @@
         <v>1</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C11" s="1">
         <v>379</v>
@@ -6272,7 +6347,7 @@
         <v>2025</v>
       </c>
       <c r="M11" s="5" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="N11" s="5">
         <f t="shared" si="10"/>
@@ -6475,7 +6550,7 @@
         <v>2</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C15" s="1">
         <v>440</v>
@@ -6546,7 +6621,7 @@
         <v>2</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C16" s="1">
         <v>440</v>
@@ -6621,7 +6696,7 @@
         <v>2</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C17" s="1">
         <v>440</v>
@@ -6656,7 +6731,7 @@
         <v>2025</v>
       </c>
       <c r="M17" s="5" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="N17" s="5">
         <f t="shared" si="10"/>
@@ -6702,7 +6777,7 @@
         <v>2</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C18" s="1">
         <v>440</v>
@@ -6718,7 +6793,7 @@
         <v>2025</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="H18" s="5">
         <f t="shared" si="2"/>
@@ -6779,7 +6854,7 @@
         <v>2</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C19" s="1">
         <v>440</v>
@@ -6795,7 +6870,7 @@
         <v>2025</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="H19" s="5">
         <f>IF((D19-E19)&lt;0,0,(D19-E19))</f>
@@ -6856,7 +6931,7 @@
         <v>2</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C20" s="32">
         <v>440</v>
@@ -6872,7 +6947,7 @@
         <v>2025</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="H20" s="5">
         <f>IF((D20-E20)&lt;0,0,(D20-E20))</f>
@@ -6893,7 +6968,7 @@
         <v>2025</v>
       </c>
       <c r="M20" s="5" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="N20" s="5">
         <f t="shared" si="10"/>
@@ -7095,7 +7170,7 @@
         <v>3</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C24" s="1">
         <v>493</v>
@@ -7166,7 +7241,7 @@
         <v>3</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C25" s="1">
         <v>493</v>
@@ -7241,7 +7316,7 @@
         <v>3</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C26" s="1">
         <v>493</v>
@@ -7255,7 +7330,7 @@
         <v>2025</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="H26" s="5">
         <f t="shared" si="2"/>
@@ -7316,7 +7391,7 @@
         <v>3</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C27" s="1">
         <v>493</v>
@@ -7332,7 +7407,7 @@
         <v>2025</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="H27" s="5">
         <f t="shared" si="2"/>
@@ -7393,7 +7468,7 @@
         <v>3</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C28" s="1">
         <v>493</v>
@@ -7409,7 +7484,7 @@
         <v>2025</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="H28" s="5">
         <f t="shared" si="2"/>
@@ -7470,7 +7545,7 @@
         <v>3</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C29" s="1">
         <v>493</v>
@@ -7486,7 +7561,7 @@
         <v>2025</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="H29" s="5">
         <f>IF((D29-E29)&lt;0,0,(D29-E29))</f>
@@ -7546,7 +7621,7 @@
         <v>3</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C30" s="1">
         <v>493</v>
@@ -7562,7 +7637,7 @@
         <v>2025</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="H30" s="5">
         <f>IF((D30-E30)&lt;0,0,(D30-E30))</f>
@@ -7708,7 +7783,7 @@
         <v>4</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C33" s="1">
         <v>550</v>
@@ -7779,7 +7854,7 @@
         <v>4</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C34" s="1">
         <v>550</v>
@@ -7850,7 +7925,7 @@
         <v>4</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C35" s="1">
         <v>550</v>
@@ -7921,7 +7996,7 @@
         <v>4</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C36" s="1">
         <v>550</v>
@@ -8063,7 +8138,7 @@
         <v>4</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C38" s="1">
         <v>550</v>
@@ -8271,7 +8346,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:27" ht="19.5">
+    <row r="41" spans="1:27" ht="38.25">
       <c r="A41" s="1">
         <v>4</v>
       </c>
@@ -8361,7 +8436,7 @@
         <v>5</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C43" s="1">
         <v>431</v>
@@ -8377,7 +8452,7 @@
         <v>2025</v>
       </c>
       <c r="G43" s="5" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="H43" s="5">
         <f t="shared" si="2"/>
@@ -8438,7 +8513,7 @@
         <v>5</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C44" s="1">
         <v>431</v>
@@ -8454,7 +8529,7 @@
         <v>2025</v>
       </c>
       <c r="G44" s="5" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="H44" s="5">
         <f t="shared" si="2"/>
@@ -8515,7 +8590,7 @@
         <v>5</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C45" s="1">
         <v>431</v>
@@ -8531,7 +8606,7 @@
         <v>2025</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="H45" s="5">
         <f t="shared" si="2"/>
@@ -8552,7 +8627,7 @@
         <v>2025</v>
       </c>
       <c r="M45" s="5" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="N45" s="5">
         <f t="shared" si="10"/>
@@ -8598,7 +8673,7 @@
         <v>5</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C46" s="1">
         <v>431</v>
@@ -8614,7 +8689,7 @@
         <v>2025</v>
       </c>
       <c r="G46" s="5" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="H46" s="5">
         <f t="shared" si="2"/>
@@ -8691,7 +8766,7 @@
         <v>2025</v>
       </c>
       <c r="G47" s="5" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="H47" s="5">
         <f t="shared" si="2"/>
@@ -8752,7 +8827,7 @@
         <v>5</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C48" s="1">
         <v>431</v>
@@ -8768,7 +8843,7 @@
         <v>2025</v>
       </c>
       <c r="G48" s="5" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="H48" s="5">
         <f t="shared" si="2"/>
@@ -8845,7 +8920,7 @@
         <v>2025</v>
       </c>
       <c r="G49" s="5" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="H49" s="5">
         <f t="shared" si="2"/>
@@ -8993,7 +9068,7 @@
         <v>2025</v>
       </c>
       <c r="G51" s="5" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="H51" s="5">
         <f t="shared" si="2"/>
@@ -9068,7 +9143,7 @@
         <v>6</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C53" s="1">
         <v>484</v>
@@ -9139,7 +9214,7 @@
         <v>6</v>
       </c>
       <c r="B54" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C54" s="1">
         <v>484</v>
@@ -9210,7 +9285,7 @@
         <v>6</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C55" s="1">
         <v>484</v>
@@ -9281,7 +9356,7 @@
         <v>6</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C56" s="1">
         <v>484</v>
@@ -9423,7 +9498,7 @@
         <v>6</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C58" s="1">
         <v>484</v>
@@ -9716,12 +9791,12 @@
       <c r="Z62" s="13"/>
       <c r="AA62" s="13"/>
     </row>
-    <row r="63" spans="1:27" ht="19.149999999999999">
+    <row r="63" spans="1:27" ht="19.5">
       <c r="A63" s="10">
         <v>7</v>
       </c>
       <c r="B63" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="12">
@@ -9790,7 +9865,7 @@
         <v>7</v>
       </c>
       <c r="B64" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C64" s="10"/>
       <c r="D64" s="12">
@@ -9859,7 +9934,7 @@
         <v>7</v>
       </c>
       <c r="B65" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="12">
@@ -10066,7 +10141,7 @@
         <v>7</v>
       </c>
       <c r="B68" s="11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C68" s="10"/>
       <c r="D68" s="12">
@@ -10356,7 +10431,7 @@
         <v>8</v>
       </c>
       <c r="B73" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="12">
@@ -10425,7 +10500,7 @@
         <v>8</v>
       </c>
       <c r="B74" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C74" s="10"/>
       <c r="D74" s="12">
@@ -10494,7 +10569,7 @@
         <v>8</v>
       </c>
       <c r="B75" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="12">
@@ -10701,7 +10776,7 @@
         <v>8</v>
       </c>
       <c r="B78" s="11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C78" s="10"/>
       <c r="D78" s="12">
@@ -10991,7 +11066,7 @@
         <v>9</v>
       </c>
       <c r="B83" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="12">
@@ -11060,7 +11135,7 @@
         <v>9</v>
       </c>
       <c r="B84" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C84" s="10"/>
       <c r="D84" s="12">
@@ -11129,7 +11204,7 @@
         <v>9</v>
       </c>
       <c r="B85" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="12">
@@ -11336,7 +11411,7 @@
         <v>9</v>
       </c>
       <c r="B88" s="11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C88" s="10"/>
       <c r="D88" s="12">
@@ -11626,7 +11701,7 @@
         <v>10</v>
       </c>
       <c r="B93" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="12">
@@ -11695,7 +11770,7 @@
         <v>10</v>
       </c>
       <c r="B94" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C94" s="10"/>
       <c r="D94" s="12">
@@ -11764,7 +11839,7 @@
         <v>10</v>
       </c>
       <c r="B95" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="12">
@@ -11971,7 +12046,7 @@
         <v>10</v>
       </c>
       <c r="B98" s="11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C98" s="10"/>
       <c r="D98" s="12">
@@ -13808,194 +13883,155 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:27">
-      <c r="J128" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="129" spans="2:13">
-      <c r="J129" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
     <row r="130" spans="2:13">
-      <c r="B130" s="48" t="s">
+      <c r="B130" s="44" t="s">
         <v>33</v>
       </c>
-      <c r="C130" s="48"/>
-      <c r="D130" s="48"/>
-      <c r="E130" s="48"/>
+      <c r="C130" s="44"/>
+      <c r="D130" s="44"/>
+      <c r="E130" s="44"/>
       <c r="F130" s="7"/>
       <c r="G130" s="7"/>
       <c r="H130" s="7"/>
       <c r="I130" s="7"/>
-      <c r="J130" s="7" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
+      <c r="J130" s="7"/>
       <c r="K130" s="7"/>
       <c r="L130" s="7"/>
       <c r="M130" s="7"/>
     </row>
     <row r="131" spans="2:13">
-      <c r="B131" s="48" t="s">
+      <c r="B131" s="44" t="s">
         <v>34</v>
       </c>
-      <c r="C131" s="48"/>
-      <c r="D131" s="48"/>
-      <c r="E131" s="48"/>
+      <c r="C131" s="44"/>
+      <c r="D131" s="44"/>
+      <c r="E131" s="44"/>
       <c r="F131" s="7"/>
       <c r="G131" s="7"/>
       <c r="H131" s="7"/>
       <c r="I131" s="7"/>
-      <c r="J131" s="7" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
+      <c r="J131" s="7"/>
       <c r="K131" s="7"/>
       <c r="L131" s="7"/>
       <c r="M131" s="7"/>
     </row>
     <row r="132" spans="2:13">
-      <c r="B132" s="48" t="s">
+      <c r="B132" s="44" t="s">
         <v>35</v>
       </c>
-      <c r="C132" s="48"/>
-      <c r="D132" s="48"/>
-      <c r="E132" s="48"/>
+      <c r="C132" s="44"/>
+      <c r="D132" s="44"/>
+      <c r="E132" s="44"/>
       <c r="F132" s="7"/>
       <c r="G132" s="7"/>
       <c r="H132" s="7"/>
       <c r="I132" s="7"/>
-      <c r="J132" s="7" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
+      <c r="J132" s="7"/>
       <c r="K132" s="7"/>
       <c r="L132" s="7"/>
       <c r="M132" s="7"/>
     </row>
     <row r="133" spans="2:13" ht="15">
-      <c r="B133" s="48"/>
-      <c r="C133" s="48"/>
-      <c r="D133" s="48"/>
-      <c r="E133" s="49" t="s">
+      <c r="B133" s="44"/>
+      <c r="C133" s="44"/>
+      <c r="D133" s="44"/>
+      <c r="E133" s="45" t="s">
         <v>36</v>
       </c>
       <c r="F133" s="7"/>
       <c r="G133" s="7"/>
       <c r="H133" s="7"/>
       <c r="I133" s="7"/>
-      <c r="J133" s="7" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
+      <c r="J133" s="7"/>
       <c r="K133" s="7"/>
       <c r="L133" s="7"/>
       <c r="M133" s="7"/>
     </row>
     <row r="134" spans="2:13" ht="15">
-      <c r="B134" s="48"/>
-      <c r="C134" s="48"/>
-      <c r="D134" s="48"/>
-      <c r="E134" s="50" t="s">
+      <c r="B134" s="44"/>
+      <c r="C134" s="44"/>
+      <c r="D134" s="44"/>
+      <c r="E134" s="46" t="s">
         <v>37</v>
       </c>
       <c r="F134" s="7"/>
       <c r="G134" s="7"/>
       <c r="H134" s="7"/>
       <c r="I134" s="7"/>
-      <c r="J134" s="7" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
+      <c r="J134" s="7"/>
       <c r="K134" s="7"/>
-      <c r="L134" s="49" t="s">
+      <c r="L134" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="M134" s="48"/>
+      <c r="M134" s="44"/>
     </row>
     <row r="135" spans="2:13">
-      <c r="B135" s="48"/>
-      <c r="C135" s="48"/>
-      <c r="D135" s="48"/>
-      <c r="E135" s="50" t="s">
+      <c r="B135" s="44"/>
+      <c r="C135" s="44"/>
+      <c r="D135" s="44"/>
+      <c r="E135" s="46" t="s">
         <v>38</v>
       </c>
       <c r="F135" s="7"/>
       <c r="G135" s="7"/>
       <c r="H135" s="7"/>
       <c r="I135" s="7"/>
-      <c r="J135" s="7" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
+      <c r="J135" s="7"/>
       <c r="K135" s="7"/>
-      <c r="L135" s="50" t="s">
+      <c r="L135" s="46" t="s">
         <v>37</v>
       </c>
-      <c r="M135" s="48"/>
+      <c r="M135" s="44"/>
     </row>
     <row r="136" spans="2:13" ht="15">
-      <c r="B136" s="51" t="s">
+      <c r="B136" s="47" t="s">
         <v>39</v>
       </c>
-      <c r="C136" s="48"/>
-      <c r="D136" s="48"/>
-      <c r="E136" s="48"/>
+      <c r="C136" s="44"/>
+      <c r="D136" s="44"/>
+      <c r="E136" s="44"/>
       <c r="F136" s="7"/>
       <c r="G136" s="7"/>
       <c r="H136" s="7"/>
       <c r="I136" s="7"/>
-      <c r="J136" s="7" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
+      <c r="J136" s="7"/>
       <c r="K136" s="7"/>
-      <c r="L136" s="50" t="s">
+      <c r="L136" s="46" t="s">
         <v>38</v>
       </c>
-      <c r="M136" s="48"/>
+      <c r="M136" s="44"/>
     </row>
     <row r="137" spans="2:13">
-      <c r="B137" s="50" t="s">
+      <c r="B137" s="46" t="s">
         <v>40</v>
       </c>
-      <c r="C137" s="48"/>
-      <c r="D137" s="48"/>
-      <c r="E137" s="48"/>
+      <c r="C137" s="44"/>
+      <c r="D137" s="44"/>
+      <c r="E137" s="44"/>
       <c r="F137" s="7"/>
       <c r="G137" s="7"/>
       <c r="H137" s="7"/>
       <c r="I137" s="7"/>
-      <c r="J137" s="7" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
+      <c r="J137" s="7"/>
       <c r="K137" s="7"/>
-      <c r="L137" s="48"/>
-      <c r="M137" s="48"/>
+      <c r="L137" s="44"/>
+      <c r="M137" s="44"/>
     </row>
     <row r="138" spans="2:13">
-      <c r="B138" s="50" t="s">
+      <c r="B138" s="46" t="s">
         <v>41</v>
       </c>
-      <c r="C138" s="48"/>
-      <c r="D138" s="48"/>
-      <c r="E138" s="48"/>
+      <c r="C138" s="44"/>
+      <c r="D138" s="44"/>
+      <c r="E138" s="44"/>
       <c r="F138" s="7"/>
       <c r="G138" s="7"/>
       <c r="H138" s="7"/>
       <c r="I138" s="7"/>
-      <c r="J138" s="7" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
+      <c r="J138" s="7"/>
       <c r="K138" s="7"/>
-      <c r="L138" s="48"/>
-      <c r="M138" s="48"/>
+      <c r="L138" s="44"/>
+      <c r="M138" s="44"/>
     </row>
     <row r="139" spans="2:13">
       <c r="B139" s="7"/>
@@ -14006,13 +14042,10 @@
       <c r="G139" s="7"/>
       <c r="H139" s="7"/>
       <c r="I139" s="7"/>
-      <c r="J139" s="7" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
+      <c r="J139" s="7"/>
       <c r="K139" s="7"/>
-      <c r="L139" s="48"/>
-      <c r="M139" s="48"/>
+      <c r="L139" s="44"/>
+      <c r="M139" s="44"/>
     </row>
     <row r="140" spans="2:13">
       <c r="B140" s="7"/>
@@ -14023,115 +14056,10 @@
       <c r="G140" s="7"/>
       <c r="H140" s="7"/>
       <c r="I140" s="7"/>
-      <c r="J140" s="7" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
+      <c r="J140" s="7"/>
       <c r="K140" s="7"/>
       <c r="L140" s="7"/>
       <c r="M140" s="7"/>
-    </row>
-    <row r="141" spans="2:13">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="2:13">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="2:13">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="2:13">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
     </row>
   </sheetData>
   <protectedRanges>
@@ -14150,8 +14078,8 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S112:S127 M112:M127 Y112:Y127 G112:G127" xr:uid="{8289B4A9-982E-4C7E-A8E2-4BF3404561DB}">
       <formula1>"CO,RO,SDO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X23:X31 X33:X41 X43:X51 X63:X71 X73:X81 X53:X61 L112:L127 X83:X91 X93:X101 X14:X21 X5:X12 L23:L31 L33:L41 L43:L51 L63:L71 L73:L81 L53:L61 R112:R127 L83:L91 L93:L101 L14:L21 L5:L12 R23:R31 R33:R41 R43:R51 R63:R71 R73:R81 R53:R61 F112:F127 R83:R91 R93:R101 R14:R21 R5:R12 X112:X127 F33:F41 F43:F51 F63:F71 F73:F81 F53:F61 F5:F12 F83:F91 F93:F101 F23:F31 F103:F110 R103:R110 L103:L110 X103:X110 F14:F21" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X112:X127 X103:X110 X93:X101 X83:X91 X73:X81 X63:X71 X53:X61 X43:X51 X33:X41 X23:X31 X14:X21 X5:X12 F112:F127 F103:F110 F93:F101 F83:F91 F73:F81 F63:F71 F53:F61 F43:F51 F33:F41 F23:F31 F14:F21 F5:F12 L112:L127 L103:L110 L93:L101 L83:L91 L73:L81 L63:L71 L53:L61 L43:L51 L33:L41 L23:L31 L14:L21 L5:L12 R112:R127 R103:R110 R93:R101 R83:R91 R73:R81 R63:R71 R53:R61 R43:R51 R33:R41 R23:R31 R14:R21 R5:R12" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M14:M110 Y14:Y110 S4:S110 G5:G12 M5:M12 Y5:Y12 G14:G21 G103:G110 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G23:G31" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
@@ -14199,38 +14127,38 @@
   <sheetData>
     <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1">
       <c r="B1" s="35"/>
-      <c r="D1" s="42" t="s">
+      <c r="D1" s="48" t="s">
         <v>42</v>
       </c>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42"/>
-      <c r="H1" s="42"/>
-      <c r="I1" s="42"/>
-      <c r="J1" s="43" t="s">
+      <c r="E1" s="48"/>
+      <c r="F1" s="48"/>
+      <c r="G1" s="48"/>
+      <c r="H1" s="48"/>
+      <c r="I1" s="48"/>
+      <c r="J1" s="49" t="s">
         <v>43</v>
       </c>
-      <c r="K1" s="43"/>
-      <c r="L1" s="43"/>
-      <c r="M1" s="43"/>
-      <c r="N1" s="43"/>
-      <c r="O1" s="43"/>
-      <c r="P1" s="44" t="s">
+      <c r="K1" s="49"/>
+      <c r="L1" s="49"/>
+      <c r="M1" s="49"/>
+      <c r="N1" s="49"/>
+      <c r="O1" s="49"/>
+      <c r="P1" s="50" t="s">
         <v>44</v>
       </c>
-      <c r="Q1" s="44"/>
-      <c r="R1" s="44"/>
-      <c r="S1" s="44"/>
-      <c r="T1" s="44"/>
-      <c r="U1" s="44"/>
-      <c r="V1" s="45" t="s">
+      <c r="Q1" s="50"/>
+      <c r="R1" s="50"/>
+      <c r="S1" s="50"/>
+      <c r="T1" s="50"/>
+      <c r="U1" s="50"/>
+      <c r="V1" s="51" t="s">
         <v>45</v>
       </c>
-      <c r="W1" s="45"/>
-      <c r="X1" s="45"/>
-      <c r="Y1" s="45"/>
-      <c r="Z1" s="45"/>
-      <c r="AA1" s="45"/>
+      <c r="W1" s="51"/>
+      <c r="X1" s="51"/>
+      <c r="Y1" s="51"/>
+      <c r="Z1" s="51"/>
+      <c r="AA1" s="51"/>
     </row>
     <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1">
       <c r="A2" s="15" t="s">
@@ -14389,7 +14317,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="5">
@@ -14458,7 +14386,7 @@
         <v>1</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="5">
@@ -14527,7 +14455,7 @@
         <v>1</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="5">
@@ -14596,7 +14524,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="5">
@@ -14665,7 +14593,7 @@
         <v>1</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="5">
@@ -14734,7 +14662,7 @@
         <v>1</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="5">
@@ -14942,7 +14870,7 @@
         <v>2</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="5">
@@ -15011,7 +14939,7 @@
         <v>2</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="5">
@@ -15080,7 +15008,7 @@
         <v>2</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="5">
@@ -15149,7 +15077,7 @@
         <v>2</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="5">
@@ -15218,7 +15146,7 @@
         <v>2</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C17" s="1"/>
       <c r="D17" s="5">
@@ -15287,7 +15215,7 @@
         <v>2</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C18" s="1"/>
       <c r="D18" s="5">
@@ -15495,7 +15423,7 @@
         <v>3</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C22" s="1"/>
       <c r="D22" s="5">
@@ -15564,7 +15492,7 @@
         <v>3</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C23" s="1"/>
       <c r="D23" s="5">
@@ -15633,7 +15561,7 @@
         <v>3</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C24" s="1"/>
       <c r="D24" s="5">
@@ -15702,7 +15630,7 @@
         <v>3</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C25" s="1"/>
       <c r="D25" s="5">
@@ -15771,7 +15699,7 @@
         <v>3</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C26" s="1"/>
       <c r="D26" s="5">
@@ -15840,7 +15768,7 @@
         <v>3</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C27" s="1"/>
       <c r="D27" s="5">
@@ -15909,7 +15837,7 @@
         <v>3</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C28" s="1"/>
       <c r="D28" s="5">
@@ -16048,7 +15976,7 @@
         <v>4</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C31" s="1"/>
       <c r="D31" s="5">
@@ -16117,7 +16045,7 @@
         <v>4</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C32" s="1"/>
       <c r="D32" s="5">
@@ -16186,7 +16114,7 @@
         <v>4</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C33" s="1"/>
       <c r="D33" s="5">
@@ -16255,7 +16183,7 @@
         <v>4</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C34" s="1"/>
       <c r="D34" s="5">
@@ -16393,7 +16321,7 @@
         <v>4</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="5">
@@ -16808,7 +16736,7 @@
         <v>5</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C43" s="1"/>
       <c r="D43" s="5">
@@ -16877,7 +16805,7 @@
         <v>5</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C44" s="1"/>
       <c r="D44" s="5">
@@ -16946,7 +16874,7 @@
         <v>5</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C45" s="1"/>
       <c r="D45" s="5">
@@ -17015,7 +16943,7 @@
         <v>5</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C46" s="1"/>
       <c r="D46" s="5">
@@ -17153,7 +17081,7 @@
         <v>5</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C48" s="1"/>
       <c r="D48" s="5">
@@ -17568,7 +17496,7 @@
         <v>6</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C55" s="1">
         <v>484</v>
@@ -17584,7 +17512,7 @@
         <v>2025</v>
       </c>
       <c r="G55" s="5" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="H55" s="5">
         <f t="shared" si="0"/>
@@ -17635,7 +17563,7 @@
         <v>2025</v>
       </c>
       <c r="Y55" s="5" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="Z55" s="5">
         <f t="shared" si="6"/>
@@ -17651,7 +17579,7 @@
         <v>6</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C56" s="1">
         <v>484</v>
@@ -17667,7 +17595,7 @@
         <v>2025</v>
       </c>
       <c r="G56" s="5" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="H56" s="5">
         <f t="shared" si="0"/>
@@ -17718,7 +17646,7 @@
         <v>2025</v>
       </c>
       <c r="Y56" s="5" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="Z56" s="5">
         <f t="shared" si="6"/>
@@ -17734,7 +17662,7 @@
         <v>6</v>
       </c>
       <c r="B57" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C57" s="1">
         <v>484</v>
@@ -17750,7 +17678,7 @@
         <v>2025</v>
       </c>
       <c r="G57" s="5" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="H57" s="5">
         <f t="shared" si="0"/>
@@ -17801,7 +17729,7 @@
         <v>2025</v>
       </c>
       <c r="Y57" s="5" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="Z57" s="5">
         <f t="shared" si="6"/>
@@ -17817,7 +17745,7 @@
         <v>6</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C58" s="1">
         <v>484</v>
@@ -17878,7 +17806,7 @@
         <v>2025</v>
       </c>
       <c r="Y58" s="5" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="Z58" s="5">
         <f t="shared" si="6"/>
@@ -17955,7 +17883,7 @@
         <v>2025</v>
       </c>
       <c r="Y59" s="5" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="Z59" s="5">
         <f t="shared" si="6"/>
@@ -17971,7 +17899,7 @@
         <v>6</v>
       </c>
       <c r="B60" s="9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C60" s="1">
         <v>484</v>
@@ -18032,7 +17960,7 @@
         <v>2025</v>
       </c>
       <c r="Y60" s="5" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="Z60" s="5">
         <f t="shared" si="6"/>
@@ -18109,7 +18037,7 @@
         <v>2025</v>
       </c>
       <c r="Y61" s="5" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="Z61" s="5">
         <f>IF((V61-W61)&lt;0,0,(V61-W61))</f>
@@ -18186,7 +18114,7 @@
         <v>2025</v>
       </c>
       <c r="Y62" s="5" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="Z62" s="5">
         <f t="shared" si="6"/>
@@ -18334,7 +18262,7 @@
         <v>2025</v>
       </c>
       <c r="Y64" s="5" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="Z64" s="5">
         <f>IF((V64-W64)&lt;0,0,(V64-W64))</f>
@@ -18411,7 +18339,7 @@
         <v>2025</v>
       </c>
       <c r="Y65" s="5" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="Z65" s="5">
         <f t="shared" si="6"/>
@@ -18428,7 +18356,7 @@
         <v>7</v>
       </c>
       <c r="B67" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="12">
@@ -18497,7 +18425,7 @@
         <v>7</v>
       </c>
       <c r="B68" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C68" s="10"/>
       <c r="D68" s="12">
@@ -18566,7 +18494,7 @@
         <v>7</v>
       </c>
       <c r="B69" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="12">
@@ -18773,7 +18701,7 @@
         <v>7</v>
       </c>
       <c r="B72" s="11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C72" s="10"/>
       <c r="D72" s="12">
@@ -19188,7 +19116,7 @@
         <v>8</v>
       </c>
       <c r="B79" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="12">
@@ -19257,7 +19185,7 @@
         <v>8</v>
       </c>
       <c r="B80" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C80" s="10"/>
       <c r="D80" s="12">
@@ -19326,7 +19254,7 @@
         <v>8</v>
       </c>
       <c r="B81" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="12">
@@ -19533,7 +19461,7 @@
         <v>8</v>
       </c>
       <c r="B84" s="11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C84" s="10"/>
       <c r="D84" s="12">
@@ -19948,7 +19876,7 @@
         <v>9</v>
       </c>
       <c r="B91" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="12">
@@ -20017,7 +19945,7 @@
         <v>9</v>
       </c>
       <c r="B92" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C92" s="10"/>
       <c r="D92" s="12">
@@ -20086,7 +20014,7 @@
         <v>9</v>
       </c>
       <c r="B93" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="12">
@@ -20293,7 +20221,7 @@
         <v>9</v>
       </c>
       <c r="B96" s="11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C96" s="10"/>
       <c r="D96" s="12">
@@ -20708,7 +20636,7 @@
         <v>10</v>
       </c>
       <c r="B103" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="12">
@@ -20777,7 +20705,7 @@
         <v>10</v>
       </c>
       <c r="B104" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C104" s="10"/>
       <c r="D104" s="12">
@@ -20846,7 +20774,7 @@
         <v>10</v>
       </c>
       <c r="B105" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C105" s="10"/>
       <c r="D105" s="12">
@@ -21053,7 +20981,7 @@
         <v>10</v>
       </c>
       <c r="B108" s="11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C108" s="10"/>
       <c r="D108" s="12">
@@ -22723,8 +22651,8 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S115:S122 Y115:Y122 G115:G122 Y3:Y10 S3:S10 M3:M10 G3:G10 G12:G19 Y12:Y19 S12:S19 M12:M19 M21:M29 G21:G29 Y21:Y29 S21:S29 S31:S41 M31:M41 G31:G41 Y31:Y41 Y43:Y53 S43:S53 M43:M53 G43:G53 G55:G65 Y55:Y65 S55:S65 M55:M65 M67:M77 G67:G77 Y67:Y77 S67:S77 S79:S89 M79:M89 G79:G89 Y79:Y89 Y91:Y101 S91:S101 M91:M101 G91:G101 G103:G113 Y103:Y113 S103:S113 M103:M113 M115:M122" xr:uid="{CBD486C7-A5DB-48F1-B496-5027CC51E830}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X21:X29 X31:X41 X43:X53 X67:X77 X79:X89 X55:X65 X91:X101 X103:X113 X12:X19 X3:X10 L21:L29 L31:L41 L43:L53 L67:L77 L79:L89 L55:L65 L91:L101 L103:L113 L12:L19 L3:L10 R21:R29 R31:R41 R43:R53 R67:R77 R79:R89 R55:R65 R91:R101 R103:R113 R12:R19 R3:R10 F21:F29 F31:F41 F43:F53 F67:F77 F79:F89 F55:F65 F3:F10 F91:F101 X115:X122 F12:F19 F115:F122 R115:R122 L115:L122 F103:F113" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X115:X122 X103:X113 X91:X101 X79:X89 X67:X77 X55:X65 X43:X53 X21:X29 X12:X19 X3:X10 X31:X41 F115:F122 F103:F113 F91:F101 F79:F89 F67:F77 F55:F65 F43:F53 F31:F41 F21:F29 F12:F19 F3:F10 L115:L122 L103:L113 L91:L101 L79:L89 L67:L77 L43:L53 L31:L41 L21:L29 L12:L19 L3:L10 L55:L65 R115:R122 R103:R113 R91:R101 R79:R89 R67:R77 R55:R65 R43:R53 R31:R41 R21:R29 R12:R19 R3:R10" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
